--- a/reports/集团总公司_现金流量表_2025-11.xlsx
+++ b/reports/集团总公司_现金流量表_2025-11.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>189150000</v>
+        <v>189361450</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>2170350000</v>
+        <v>2168800200</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3878756</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>44652281</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1951924</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>22298807</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>967700</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>11159872</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>781670</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>8922958</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>580535</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>6692958</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>390494</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>4463508</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>290795</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>3345077</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>194750</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>2232509</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>486133</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>5573885</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>243906</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2805184</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>155032</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1772323</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>514100</v>
+        <v>511963</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>5898900</v>
+        <v>5901877</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3492000</v>
+        <v>3508851</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>40068000</v>
+        <v>40055301</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>193156100</v>
+        <v>203303959</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>116400000</v>
+        <v>116277710</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1335600000</v>
+        <v>1334723591</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1295576</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>14884723</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>974292</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>11147862</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>645916</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>7441544</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>488267</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>5575299</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>322476</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>3719452</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>245509</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2803143</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>23474000</v>
+        <v>23370493</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>269346000</v>
+        <v>269289846</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>10864000</v>
+        <v>10901227</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>124656000</v>
+        <v>124707812</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>4947000</v>
+        <v>4936681</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>56763000</v>
+        <v>56730116</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>155685000</v>
+        <v>159458147</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>37471100</v>
+        <v>43845812</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>240000</v>
+        <v>238844</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2640000</v>
+        <v>2639864</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2100000</v>
+        <v>2093655</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>23100000</v>
+        <v>23088758</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1280000</v>
+        <v>1282038</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>14080000</v>
+        <v>14089000</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2340000</v>
+        <v>2332499</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20000000</v>
+        <v>19968026</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>220000000</v>
+        <v>220161491</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2900000</v>
+        <v>2908777</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>31900000</v>
+        <v>31878723</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14200000</v>
+        <v>14141233</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>156200000</v>
+        <v>156282811</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>520000</v>
+        <v>518017</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>5720000</v>
+        <v>5717972</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>20520000</v>
+        <v>20486043</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18180000</v>
+        <v>-18153544</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4700000</v>
+        <v>4709832</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>51700000</v>
+        <v>51662761</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7500000</v>
+        <v>7533095</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>82500000</v>
+        <v>82461016</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7500000</v>
+        <v>7463008</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>82500000</v>
+        <v>82521966</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>240000</v>
+        <v>241185</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2640000</v>
+        <v>2639916</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12440000</v>
+        <v>12484112</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6100000</v>
+        <v>6121041</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>67100000</v>
+        <v>67128265</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6100000</v>
+        <v>6087105</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>67100000</v>
+        <v>67060200</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1000000</v>
+        <v>1000557</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>11000000</v>
+        <v>11007733</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>870000</v>
+        <v>867772</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>9570000</v>
+        <v>9576685</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>125000</v>
+        <v>125475</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1375000</v>
+        <v>1374199</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7225000</v>
+        <v>7247073</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5215000</v>
+        <v>5237039</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>24506100</v>
+        <v>30929307</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>24506100</v>
+        <v>30929307</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
